--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488293_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488293_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6527</v>
+        <v>4.6571</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0847</v>
+        <v>4.966</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.432</v>
+        <v>-0.3089</v>
       </c>
       <c r="G2" t="n">
         <v>4.8676</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4002</v>
+        <v>-0.3958</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2584</v>
+        <v>-0.3771</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1418</v>
+        <v>-0.0187</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9037</v>
+        <v>1.3893</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4908</v>
+        <v>-1.4408</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4129</v>
+        <v>2.8301</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0853</v>
+        <v>0.9877</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4979</v>
+        <v>-1.1705</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5831</v>
+        <v>2.1581</v>
       </c>
       <c r="J3" t="n">
-        <v>2.427</v>
+        <v>0.9611</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0946</v>
+        <v>-0.4596</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5216</v>
+        <v>1.4207</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3417</v>
+        <v>0.0266</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4033</v>
+        <v>-0.7108</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0616</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.0382</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4087</v>
+        <v>2.0382</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3917</v>
+        <v>0.401</v>
       </c>
       <c r="T3" t="n">
-        <v>0.102</v>
+        <v>-0.3637</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2897</v>
+        <v>0.7648</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9439</v>
+        <v>0.0005</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9439</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.462</v>
+        <v>1.3637</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2449</v>
+        <v>0.197</v>
       </c>
       <c r="F4" t="n">
-        <v>2.707</v>
+        <v>1.1667</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9877</v>
+        <v>2.0853</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1705</v>
+        <v>-0.4979</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1581</v>
+        <v>2.5831</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9611</v>
+        <v>2.427</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4596</v>
+        <v>-0.0946</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4207</v>
+        <v>2.5216</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0266</v>
+        <v>-0.3417</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7108</v>
+        <v>-0.4033</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.0616</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.0382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0382</v>
+        <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4738</v>
+        <v>-0.1483</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1679</v>
+        <v>-0.1918</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.0435</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0005</v>
+        <v>-0.9439</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="5">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7194</v>
+        <v>-0.5235</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3851</v>
+        <v>-1.1893</v>
       </c>
       <c r="F7" t="n">
         <v>0.6657999999999999</v>
@@ -1000,10 +1000,10 @@
         <v>1.6676</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2189</v>
+        <v>-0.023</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3867</v>
+        <v>-0.1909</v>
       </c>
       <c r="U7" t="n">
         <v>0.1679</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0452</v>
+        <v>-1.7695</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8739</v>
+        <v>-2.3167</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8288</v>
+        <v>0.5472</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2509</v>
+        <v>-1.68</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.7026</v>
+        <v>0.2983</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4517</v>
+        <v>-1.9783</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.0306</v>
+        <v>-0.2537</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.1136</v>
+        <v>0.1503</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0829</v>
+        <v>-0.404</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2203</v>
+        <v>-1.4263</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.589</v>
+        <v>0.148</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3687</v>
+        <v>-1.5743</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9264</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9264</v>
+        <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1322</v>
+        <v>0.281</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0096</v>
+        <v>-0.2101</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1226</v>
+        <v>0.4912</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2844</v>
+        <v>-2.4654</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7085</v>
+        <v>-3.2449</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4241</v>
+        <v>0.7795</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.68</v>
+        <v>-2.2509</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2983</v>
+        <v>-2.7026</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9783</v>
+        <v>0.4517</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2537</v>
+        <v>-2.0306</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1503</v>
+        <v>-2.1136</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.404</v>
+        <v>0.0829</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4263</v>
+        <v>-0.2203</v>
       </c>
       <c r="N9" t="n">
-        <v>0.148</v>
+        <v>-0.589</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5743</v>
+        <v>0.3687</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3706</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2338</v>
+        <v>0.7119</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6019</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3681</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6317</v>
+        <v>-2.7542</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.172</v>
+        <v>-2.2699</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4597</v>
+        <v>-0.4843</v>
       </c>
       <c r="G10" t="n">
         <v>0.8289</v>
@@ -1234,13 +1234,13 @@
         <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5394</v>
+        <v>0.4169</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0037</v>
+        <v>-0.1016</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5432</v>
+        <v>0.5185</v>
       </c>
       <c r="V10" t="n">
         <v>-2.5177</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4667</v>
+        <v>-3.0263</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5488</v>
+        <v>-3.0592</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0328</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8462</v>
@@ -1312,13 +1312,13 @@
         <v>2.2234</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5464</v>
+        <v>-0.106</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.0612</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0045</v>
+        <v>-0.0448</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2594</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2808</v>
+        <v>-3.2806</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.1082</v>
+        <v>-9.1083</v>
       </c>
       <c r="F12" t="n">
-        <v>5.827599999999999</v>
+        <v>5.8275</v>
       </c>
       <c r="G12" t="n">
         <v>6.526500000000002</v>
@@ -1375,7 +1375,7 @@
         <v>-5.419</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.034800000000001</v>
+        <v>-6.0348</v>
       </c>
       <c r="O12" t="n">
         <v>0.6158000000000001</v>
@@ -1390,10 +1390,10 @@
         <v>16.6758</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1378</v>
+        <v>1.1377</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2993</v>
+        <v>-1.2992</v>
       </c>
       <c r="U12" t="n">
         <v>2.4372</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.137499999999999</v>
+        <v>9.040100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9587</v>
+        <v>6.7629</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1787</v>
+        <v>2.2772</v>
       </c>
       <c r="G13" t="n">
         <v>6.0484</v>
@@ -1468,13 +1468,13 @@
         <v>2.9646</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7185</v>
+        <v>0.6211</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2114</v>
+        <v>0.0156</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5071</v>
+        <v>0.6056</v>
       </c>
       <c r="V13" t="n">
         <v>1.2589</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4071</v>
+        <v>5.9169</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7146</v>
+        <v>3.3228</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6925</v>
+        <v>2.594</v>
       </c>
       <c r="G14" t="n">
         <v>2.5872</v>
@@ -1546,13 +1546,13 @@
         <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.4589</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4303</v>
+        <v>0.0386</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5188</v>
+        <v>0.4203</v>
       </c>
       <c r="V14" t="n">
         <v>1.5738</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0899</v>
+        <v>1.8207</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7914</v>
+        <v>-1.0851</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8812</v>
+        <v>2.9058</v>
       </c>
       <c r="G15" t="n">
         <v>0.7274</v>
@@ -1624,13 +1624,13 @@
         <v>3.7057</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1047</v>
+        <v>-0.1645</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1169</v>
+        <v>-0.4107</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2216</v>
+        <v>0.2462</v>
       </c>
       <c r="V15" t="n">
         <v>1.2578</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4482</v>
+        <v>0.042</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1362</v>
+        <v>0.5279</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5844</v>
+        <v>-0.486</v>
       </c>
       <c r="G18" t="n">
         <v>0.0383</v>
@@ -1858,13 +1858,13 @@
         <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6543</v>
+        <v>-0.1641</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8754</v>
+        <v>-0.4837</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2211</v>
+        <v>0.3196</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9439</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5191</v>
+        <v>-1.3971</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.0962</v>
+        <v>-2.9003</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5771</v>
+        <v>1.5032</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0953</v>
@@ -1936,13 +1936,13 @@
         <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3862</v>
+        <v>-0.2643</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4924</v>
+        <v>-0.2966</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1062</v>
+        <v>0.0323</v>
       </c>
       <c r="V19" t="n">
         <v>1.8888</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7234</v>
+        <v>-1.8686</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9588</v>
+        <v>-1.2208</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2355</v>
+        <v>-0.6478</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1266</v>
+        <v>-3.703</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.159</v>
+        <v>-0.6494</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9676</v>
+        <v>-3.0537</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1022</v>
+        <v>-2.1922</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4677</v>
+        <v>-0.2751</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5699</v>
+        <v>-1.9171</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0244</v>
+        <v>-1.5108</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6267</v>
+        <v>-0.3743</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3977</v>
+        <v>-1.1366</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2736</v>
+        <v>-0.6653</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0037</v>
+        <v>-0.6019</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2773</v>
+        <v>-0.0634</v>
       </c>
       <c r="V20" t="n">
-        <v>0.315</v>
+        <v>1.5733</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X20" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0656</v>
+        <v>-2.1654</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2208</v>
+        <v>-2.1547</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8448</v>
+        <v>-0.0108</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.703</v>
+        <v>-2.1266</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6494</v>
+        <v>-0.159</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.0537</v>
+        <v>-1.9676</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1922</v>
+        <v>-0.1022</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2751</v>
+        <v>0.4677</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9171</v>
+        <v>-0.5699</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5108</v>
+        <v>-2.0244</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3743</v>
+        <v>-0.6267</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1366</v>
+        <v>-1.3977</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8623</v>
+        <v>-0.1685</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6019</v>
+        <v>-0.1996</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2604</v>
+        <v>0.0311</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5733</v>
+        <v>0.315</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. PINA FURTADO</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5991</v>
+        <v>-4.0785</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9785</v>
+        <v>-4.8439</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3794</v>
+        <v>0.7654</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9873</v>
+        <v>-3.6596</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4222</v>
+        <v>-0.5443</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5651</v>
+        <v>-3.1153</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.1261</v>
+        <v>-2.7262</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.3748</v>
+        <v>-0.0946</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7512</v>
+        <v>-2.6316</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8612</v>
+        <v>-0.9334</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0474</v>
+        <v>-0.4497</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8138</v>
+        <v>-0.4837</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7793</v>
+        <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2418</v>
+        <v>-0.475</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.332</v>
+        <v>-0.2649</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0902</v>
+        <v>-0.2102</v>
       </c>
       <c r="V22" t="n">
-        <v>0.63</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>E. PINA FURTADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6425</v>
+        <v>-4.6735</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2356</v>
+        <v>-4.8806</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5931</v>
+        <v>0.2071</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6596</v>
+        <v>-4.9873</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5443</v>
+        <v>-2.4222</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.1153</v>
+        <v>-2.5651</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7262</v>
+        <v>-3.1261</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0946</v>
+        <v>-1.3748</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6316</v>
+        <v>-1.7512</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9334</v>
+        <v>-1.8612</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4497</v>
+        <v>-1.0474</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4837</v>
+        <v>-0.8138</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2234</v>
+        <v>2.7793</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0391</v>
+        <v>-0.3162</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6566</v>
+        <v>-0.2341</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3825</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.280799999999997</v>
+        <v>3.280800000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.827599999999999</v>
+        <v>-5.827600000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>9.1083</v>
+        <v>9.1081</v>
       </c>
       <c r="G24" t="n">
         <v>-6.526299999999999</v>
@@ -2299,19 +2299,19 @@
         <v>-4.8001</v>
       </c>
       <c r="J24" t="n">
-        <v>5.418999999999999</v>
+        <v>5.419</v>
       </c>
       <c r="K24" t="n">
         <v>6.034899999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6158000000000006</v>
+        <v>-0.6158000000000003</v>
       </c>
       <c r="M24" t="n">
         <v>-11.9454</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.7613</v>
+        <v>-7.761299999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-4.1842</v>
@@ -2326,16 +2326,16 @@
         <v>20.3815</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.137799999999999</v>
+        <v>-1.1379</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.4372</v>
+        <v>-2.4373</v>
       </c>
       <c r="U24" t="n">
         <v>1.2994</v>
       </c>
       <c r="V24" t="n">
-        <v>7.2393</v>
+        <v>7.239300000000001</v>
       </c>
       <c r="W24" t="n">
         <v>7.866699999999999</v>
